--- a/research/traditional_assets/database/data/luxembourg/luxembourg_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_hotel_gaming.xlsx
@@ -587,35 +587,32 @@
           <t>Hotel/Gaming</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.142</v>
-      </c>
       <c r="G2">
-        <v>-0.2826267664172901</v>
+        <v>-0.5961698584512906</v>
       </c>
       <c r="H2">
-        <v>-0.2826267664172901</v>
+        <v>-0.7127393838467944</v>
       </c>
       <c r="I2">
-        <v>-0.2671100027708507</v>
+        <v>-0.2947543713572023</v>
       </c>
       <c r="J2">
-        <v>-0.2671100027708507</v>
+        <v>-0.2947543713572023</v>
       </c>
       <c r="K2">
-        <v>-162.1</v>
+        <v>-112.6</v>
       </c>
       <c r="L2">
-        <v>-0.4491548905513993</v>
+        <v>-0.4687760199833472</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0168222003929273</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.0608348134991119</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,64 +624,73 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>6.85</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>49.51000000000001</v>
+        <v>204.2</v>
       </c>
       <c r="V2">
-        <v>0.03164993926996101</v>
+        <v>0.5014734774066797</v>
+      </c>
+      <c r="W2">
+        <v>3.849997436597518</v>
       </c>
       <c r="X2">
-        <v>0.05962337509148875</v>
+        <v>0.08566077704747807</v>
+      </c>
+      <c r="Y2">
+        <v>3.76433665955004</v>
       </c>
       <c r="Z2">
-        <v>1.790178571428571</v>
+        <v>5.11063829787234</v>
       </c>
       <c r="AB2">
-        <v>0.05864191846443415</v>
+        <v>0.08251036687920761</v>
       </c>
       <c r="AD2">
-        <v>582.75</v>
+        <v>38.37</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>582.75</v>
+        <v>38.37</v>
       </c>
       <c r="AG2">
-        <v>533.24</v>
+        <v>-165.83</v>
       </c>
       <c r="AH2">
-        <v>0.2714189236394122</v>
+        <v>0.08611441524339609</v>
       </c>
       <c r="AI2">
-        <v>0.6981382978723404</v>
+        <v>0.1029044975460616</v>
       </c>
       <c r="AJ2">
-        <v>0.2542216119835617</v>
+        <v>-0.6870364999792846</v>
       </c>
       <c r="AK2">
-        <v>0.6791049528151705</v>
+        <v>-0.9831623880950967</v>
       </c>
       <c r="AL2">
-        <v>33.066</v>
+        <v>0.033</v>
       </c>
       <c r="AM2">
-        <v>33.066</v>
+        <v>-29.567</v>
       </c>
       <c r="AN2">
-        <v>-6.272874058127018</v>
+        <v>-0.6158908507223115</v>
       </c>
       <c r="AO2">
-        <v>-2.915381358495131</v>
+        <v>-2145.454545454545</v>
       </c>
       <c r="AP2">
-        <v>-5.739935414424112</v>
+        <v>2.661797752808988</v>
       </c>
       <c r="AQ2">
-        <v>-2.915381358495131</v>
+        <v>2.394561504379883</v>
       </c>
     </row>
     <row r="3">
@@ -695,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eDreams ODIGEO S.A. (BME:EDR)</t>
+          <t>HomeToGo SE (DB:HTG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -703,35 +709,32 @@
           <t>Hotel/Gaming</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.142</v>
-      </c>
       <c r="G3">
-        <v>-0.3186440677966101</v>
+        <v>-0.790311418685121</v>
       </c>
       <c r="H3">
-        <v>-0.3186440677966101</v>
+        <v>-0.9840830449826988</v>
       </c>
       <c r="I3">
-        <v>-0.2666666666666667</v>
+        <v>-0.2166089965397924</v>
       </c>
       <c r="J3">
-        <v>-0.2666666666666667</v>
+        <v>-0.2166089965397924</v>
       </c>
       <c r="K3">
-        <v>-135.1</v>
+        <v>-37.8</v>
       </c>
       <c r="L3">
-        <v>-0.5088512241054614</v>
+        <v>-0.2615916955017301</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>6.85</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02355570839064649</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.1812169312169312</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -743,76 +746,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>6.85</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>41.7</v>
+        <v>115.8</v>
       </c>
       <c r="V3">
-        <v>0.03225806451612903</v>
+        <v>0.3982118294360385</v>
       </c>
       <c r="W3">
-        <v>-0.345966709346991</v>
+        <v>-0.1079383209594517</v>
       </c>
       <c r="X3">
-        <v>0.06597210907512528</v>
+        <v>0.0870207512261386</v>
       </c>
       <c r="Y3">
-        <v>-0.4119388184221163</v>
+        <v>-0.1949590721855903</v>
       </c>
       <c r="Z3">
-        <v>1.316964285714286</v>
+        <v>3.074468085106383</v>
       </c>
       <c r="AA3">
-        <v>-0.3511904761904762</v>
+        <v>-0.6659574468085107</v>
       </c>
       <c r="AB3">
-        <v>0.06415756495673361</v>
+        <v>0.08220773248172647</v>
       </c>
       <c r="AC3">
-        <v>-0.4153480411472098</v>
+        <v>-0.7481651792902371</v>
       </c>
       <c r="AD3">
-        <v>581.4</v>
+        <v>34.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>581.4</v>
+        <v>34.2</v>
       </c>
       <c r="AG3">
-        <v>539.6999999999999</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.3102289098767408</v>
+        <v>0.1052307692307692</v>
       </c>
       <c r="AI3">
-        <v>0.68984337921215</v>
+        <v>0.1086749285033365</v>
       </c>
       <c r="AJ3">
-        <v>0.2945317616240995</v>
+        <v>-0.390057361376673</v>
       </c>
       <c r="AK3">
-        <v>0.6736986643365372</v>
+        <v>-0.4102564102564102</v>
       </c>
       <c r="AL3">
-        <v>32.4</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>32.4</v>
+        <v>-29.6</v>
       </c>
       <c r="AN3">
-        <v>-8.651785714285714</v>
-      </c>
-      <c r="AO3">
-        <v>-2.185185185185185</v>
+        <v>-1.493449781659389</v>
       </c>
       <c r="AP3">
-        <v>-8.031249999999998</v>
+        <v>3.563318777292576</v>
       </c>
       <c r="AQ3">
-        <v>-2.185185185185185</v>
+        <v>1.057432432432432</v>
       </c>
     </row>
     <row r="4">
@@ -832,22 +835,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.1823899371069182</v>
+        <v>-0.303030303030303</v>
       </c>
       <c r="H4">
-        <v>-0.1823899371069182</v>
+        <v>-0.303030303030303</v>
       </c>
       <c r="I4">
-        <v>-0.2683438155136268</v>
+        <v>-0.412748171368861</v>
       </c>
       <c r="J4">
-        <v>-0.2683438155136268</v>
+        <v>-0.412748171368861</v>
       </c>
       <c r="K4">
-        <v>-27</v>
+        <v>-74.8</v>
       </c>
       <c r="L4">
-        <v>-0.2830188679245283</v>
+        <v>-0.7816091954022988</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -871,58 +874,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>7.81</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="V4">
-        <v>0.02875552282768777</v>
+        <v>0.7594501718213058</v>
+      </c>
+      <c r="W4">
+        <v>7.807933194154488</v>
       </c>
       <c r="X4">
-        <v>0.05327464110785222</v>
+        <v>0.08430080286881755</v>
+      </c>
+      <c r="Y4">
+        <v>7.723632391285671</v>
       </c>
       <c r="AB4">
-        <v>0.05312627197213469</v>
+        <v>0.08281300127668875</v>
       </c>
       <c r="AD4">
-        <v>1.35</v>
+        <v>4.17</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.35</v>
+        <v>4.17</v>
       </c>
       <c r="AG4">
-        <v>-6.459999999999999</v>
+        <v>-84.23</v>
       </c>
       <c r="AH4">
-        <v>0.004945960798681076</v>
+        <v>0.03458571784025877</v>
       </c>
       <c r="AI4">
-        <v>-0.1670792079207921</v>
+        <v>0.07168643630737494</v>
       </c>
       <c r="AJ4">
-        <v>-0.02436448668627894</v>
+        <v>-2.618277898663351</v>
       </c>
       <c r="AK4">
-        <v>0.4065449968533669</v>
+        <v>2.786304995038042</v>
       </c>
       <c r="AL4">
-        <v>0.666</v>
+        <v>0.033</v>
       </c>
       <c r="AM4">
-        <v>0.666</v>
+        <v>0.033</v>
       </c>
       <c r="AN4">
-        <v>-0.05252918287937744</v>
+        <v>-0.1058375634517767</v>
       </c>
       <c r="AO4">
-        <v>-38.43843843843844</v>
+        <v>-1196.969696969697</v>
       </c>
       <c r="AP4">
-        <v>0.2513618677042802</v>
+        <v>2.137817258883249</v>
       </c>
       <c r="AQ4">
-        <v>-38.43843843843844</v>
+        <v>-1196.969696969697</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_hotel_gaming.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.5961698584512906</v>
+        <v>-0.2465667915106118</v>
       </c>
       <c r="H2">
-        <v>-0.7127393838467944</v>
+        <v>-0.3583021223470662</v>
       </c>
       <c r="I2">
-        <v>-0.2947543713572023</v>
+        <v>-0.2980649188514357</v>
       </c>
       <c r="J2">
-        <v>-0.2947543713572023</v>
+        <v>-0.2980649188514357</v>
       </c>
       <c r="K2">
-        <v>-112.6</v>
+        <v>-80.59999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.4687760199833472</v>
+        <v>-0.2515605493133583</v>
       </c>
       <c r="M2">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0168222003929273</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.0608348134991119</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,73 +624,70 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>6.85</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>204.2</v>
+        <v>139.5</v>
       </c>
       <c r="V2">
-        <v>0.5014734774066797</v>
+        <v>0.2905039566847147</v>
       </c>
       <c r="W2">
-        <v>3.849997436597518</v>
+        <v>-0.3887227618320055</v>
       </c>
       <c r="X2">
-        <v>0.08566077704747807</v>
+        <v>0.0741926958886292</v>
       </c>
       <c r="Y2">
-        <v>3.76433665955004</v>
+        <v>-0.4629154577206347</v>
       </c>
       <c r="Z2">
-        <v>5.11063829787234</v>
+        <v>1.720730397422127</v>
       </c>
       <c r="AB2">
-        <v>0.08251036687920761</v>
+        <v>0.07287549651088709</v>
       </c>
       <c r="AD2">
-        <v>38.37</v>
+        <v>22.21</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>38.37</v>
+        <v>22.21</v>
       </c>
       <c r="AG2">
-        <v>-165.83</v>
+        <v>-117.29</v>
       </c>
       <c r="AH2">
-        <v>0.08611441524339609</v>
+        <v>0.04420692263290938</v>
       </c>
       <c r="AI2">
-        <v>0.1029044975460616</v>
+        <v>0.06986253971249724</v>
       </c>
       <c r="AJ2">
-        <v>-0.6870364999792846</v>
+        <v>-0.3231930781736519</v>
       </c>
       <c r="AK2">
-        <v>-0.9831623880950967</v>
+        <v>-0.6574183061487583</v>
       </c>
       <c r="AL2">
-        <v>0.033</v>
+        <v>8.1</v>
       </c>
       <c r="AM2">
-        <v>-29.567</v>
+        <v>6.723999999999999</v>
       </c>
       <c r="AN2">
-        <v>-0.6158908507223115</v>
+        <v>-0.2588578088578088</v>
       </c>
       <c r="AO2">
-        <v>-2145.454545454545</v>
+        <v>-11.79012345679012</v>
       </c>
       <c r="AP2">
-        <v>2.661797752808988</v>
+        <v>1.367016317016317</v>
       </c>
       <c r="AQ2">
-        <v>2.394561504379883</v>
+        <v>-14.20285544318858</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HomeToGo SE (DB:HTG)</t>
+          <t>HomeToGo SE (XTRA:HTG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,31 +707,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.790311418685121</v>
+        <v>-0.1204747774480712</v>
       </c>
       <c r="H3">
-        <v>-0.9840830449826988</v>
+        <v>-0.3329376854599407</v>
       </c>
       <c r="I3">
-        <v>-0.2166089965397924</v>
+        <v>-0.3002967359050445</v>
       </c>
       <c r="J3">
-        <v>-0.2166089965397924</v>
+        <v>-0.3002967359050445</v>
       </c>
       <c r="K3">
-        <v>-37.8</v>
+        <v>-47.9</v>
       </c>
       <c r="L3">
-        <v>-0.2615916955017301</v>
+        <v>-0.2842729970326409</v>
       </c>
       <c r="M3">
-        <v>6.85</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.02355570839064649</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.1812169312169312</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,76 +743,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>6.85</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>115.8</v>
+        <v>90</v>
       </c>
       <c r="V3">
-        <v>0.3982118294360385</v>
+        <v>0.2593659942363112</v>
       </c>
       <c r="W3">
-        <v>-0.1079383209594517</v>
+        <v>-0.1707664884135472</v>
       </c>
       <c r="X3">
-        <v>0.0870207512261386</v>
+        <v>0.07466909311719461</v>
       </c>
       <c r="Y3">
-        <v>-0.1949590721855903</v>
+        <v>-0.2454355815307418</v>
       </c>
       <c r="Z3">
-        <v>3.074468085106383</v>
+        <v>0.9049409237379162</v>
       </c>
       <c r="AA3">
-        <v>-0.6659574468085107</v>
+        <v>-0.2717508055853921</v>
       </c>
       <c r="AB3">
-        <v>0.08220773248172647</v>
+        <v>0.07271779014311655</v>
       </c>
       <c r="AC3">
-        <v>-0.7481651792902371</v>
+        <v>-0.3444685957285086</v>
       </c>
       <c r="AD3">
-        <v>34.2</v>
+        <v>19.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>34.2</v>
+        <v>19.6</v>
       </c>
       <c r="AG3">
-        <v>-81.59999999999999</v>
+        <v>-70.40000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1052307692307692</v>
+        <v>0.05346426623022368</v>
       </c>
       <c r="AI3">
-        <v>0.1086749285033365</v>
+        <v>0.06719232087761398</v>
       </c>
       <c r="AJ3">
-        <v>-0.390057361376673</v>
+        <v>-0.2545191612436732</v>
       </c>
       <c r="AK3">
-        <v>-0.4102564102564102</v>
+        <v>-0.3490332176499752</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AM3">
-        <v>-29.6</v>
+        <v>8.033999999999999</v>
       </c>
       <c r="AN3">
-        <v>-1.493449781659389</v>
+        <v>-0.4815724815724816</v>
+      </c>
+      <c r="AO3">
+        <v>-6.246913580246914</v>
       </c>
       <c r="AP3">
-        <v>3.563318777292576</v>
+        <v>1.72972972972973</v>
       </c>
       <c r="AQ3">
-        <v>1.057432432432432</v>
+        <v>-6.298232511824746</v>
       </c>
     </row>
     <row r="4">
@@ -835,22 +832,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.303030303030303</v>
+        <v>-0.3864384463462804</v>
       </c>
       <c r="H4">
-        <v>-0.303030303030303</v>
+        <v>-0.3864384463462804</v>
       </c>
       <c r="I4">
-        <v>-0.412748171368861</v>
+        <v>-0.2955892034233048</v>
       </c>
       <c r="J4">
-        <v>-0.412748171368861</v>
+        <v>-0.2955892034233048</v>
       </c>
       <c r="K4">
-        <v>-74.8</v>
+        <v>-32.7</v>
       </c>
       <c r="L4">
-        <v>-0.7816091954022988</v>
+        <v>-0.2152732060566162</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,64 +871,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>88.40000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="V4">
-        <v>0.7594501718213058</v>
+        <v>0.3716216216216217</v>
       </c>
       <c r="W4">
-        <v>7.807933194154488</v>
+        <v>-0.6066790352504638</v>
       </c>
       <c r="X4">
-        <v>0.08430080286881755</v>
+        <v>0.07371629866006379</v>
       </c>
       <c r="Y4">
-        <v>7.723632391285671</v>
+        <v>-0.6803953339105276</v>
       </c>
       <c r="AB4">
-        <v>0.08281300127668875</v>
+        <v>0.07303320287865765</v>
       </c>
       <c r="AD4">
-        <v>4.17</v>
+        <v>2.61</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4.17</v>
+        <v>2.61</v>
       </c>
       <c r="AG4">
-        <v>-84.23</v>
+        <v>-46.89</v>
       </c>
       <c r="AH4">
-        <v>0.03458571784025877</v>
+        <v>0.01921802518223989</v>
       </c>
       <c r="AI4">
-        <v>0.07168643630737494</v>
+        <v>0.0995803128576879</v>
       </c>
       <c r="AJ4">
-        <v>-2.618277898663351</v>
+        <v>-0.5432742440041711</v>
       </c>
       <c r="AK4">
-        <v>2.786304995038042</v>
+        <v>2.013310433662516</v>
       </c>
       <c r="AL4">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.033</v>
+        <v>-1.31</v>
       </c>
       <c r="AN4">
-        <v>-0.1058375634517767</v>
-      </c>
-      <c r="AO4">
-        <v>-1196.969696969697</v>
+        <v>-0.05787139689578714</v>
       </c>
       <c r="AP4">
-        <v>2.137817258883249</v>
+        <v>1.039689578713969</v>
       </c>
       <c r="AQ4">
-        <v>-1196.969696969697</v>
+        <v>34.27480916030534</v>
       </c>
     </row>
   </sheetData>
